--- a/data/workbook.xlsx
+++ b/data/workbook.xlsx
@@ -516,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD9"/>
+  <dimension ref="A1:AD11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1470,6 +1470,246 @@
         <v>434</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>INBLR4</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>4777132</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>06-JUL-26</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>262901070500</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>85365010</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1SFL451022R8000 UA110-30-00 220-230V 50H Z
+230-240V 60H CONTACTOR</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>PCS</t>
+        </is>
+      </c>
+      <c r="L10" s="6" t="n">
+        <v>2300.17</v>
+      </c>
+      <c r="M10" s="6" t="n">
+        <v>46003.4</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>853699B</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v>234322.87</v>
+      </c>
+      <c r="S10" s="6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T10" s="6" t="n">
+        <v>3280.52</v>
+      </c>
+      <c r="U10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>NOS</t>
+        </is>
+      </c>
+      <c r="AC10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD10" s="6" t="n">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>INBLR4</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>4777132</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>06-JUL-26</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>262901070499</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>85365010</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1SFL4510248000 UA110-30-00RA 220-230V 50 HZ
+CONTACTOR</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>PCS</t>
+        </is>
+      </c>
+      <c r="L11" s="6" t="n">
+        <v>3068.63</v>
+      </c>
+      <c r="M11" s="6" t="n">
+        <v>15343.15</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>853699B</t>
+        </is>
+      </c>
+      <c r="Q11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v>64158.48</v>
+      </c>
+      <c r="S11" s="6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T11" s="6" t="n">
+        <v>898.22</v>
+      </c>
+      <c r="U11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>NOS</t>
+        </is>
+      </c>
+      <c r="AC11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD11" s="6" t="n">
+        <v>449</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="N2:W2"/>
